--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wpi0-my.sharepoint.com/personal/jwbuchta_wpi_edu/Documents/Jobs/academic_technician/flashing_led/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0951116-67F1-40C3-973A-4194F0D3E6F0}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="11_F25DC773A252ABDACC10483079DB61465BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89E6D603-529F-4EF6-B323-A7F9519F20EC}"/>
   <bookViews>
-    <workbookView xWindow="58920" yWindow="870" windowWidth="24900" windowHeight="13830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>No charging CR2450</t>
   </si>
@@ -102,6 +102,54 @@
   </si>
   <si>
     <t>C2150</t>
+  </si>
+  <si>
+    <t>Second Revision</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Bulk AAs</t>
+  </si>
+  <si>
+    <t>Link / pn</t>
+  </si>
+  <si>
+    <t>https://a.co/d/etzIdbg</t>
+  </si>
+  <si>
+    <t>Qty per board</t>
+  </si>
+  <si>
+    <t>AA Holder</t>
+  </si>
+  <si>
+    <t>https://a.co/d/iyl8QFg</t>
+  </si>
+  <si>
+    <t>C5947</t>
+  </si>
+  <si>
+    <t>Shift Register</t>
+  </si>
+  <si>
+    <t>C2678753</t>
+  </si>
+  <si>
+    <t>PCA9635</t>
+  </si>
+  <si>
+    <t>Assuming 50-60 boards</t>
+  </si>
+  <si>
+    <t>STM32F030</t>
+  </si>
+  <si>
+    <t>C62514</t>
+  </si>
+  <si>
+    <t>Total / board</t>
   </si>
 </sst>
 </file>
@@ -123,12 +171,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,8 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,12 +480,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G15"/>
+  <dimension ref="B2:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="16.89453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7890625" customWidth="1"/>
     <col min="4" max="4" width="13.3671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
@@ -605,9 +661,161 @@
         <v>220.67</v>
       </c>
     </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>0.15</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <f>C20*D20</f>
+        <v>0.3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>0.38</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <f>C21*D21</f>
+        <v>0.38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ref="E22:E29" si="1">C22*D22</f>
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>1.2645</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>3.7934999999999999</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24">
+        <v>0.54149999999999998</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>0.54149999999999998</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30">
+        <f>SUM(E20:E29)</f>
+        <v>5.1067999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
